--- a/数据表/Role.xlsx
+++ b/数据表/Role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19950" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1022,8 +1022,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.109421052631579"/>
-          <c:y val="0.0164073071718539"/>
+          <c:x val="0.109005112072355"/>
+          <c:y val="0.0707678883071553"/>
           <c:w val="0.852421052631579"/>
           <c:h val="0.580672079386558"/>
         </c:manualLayout>
@@ -2041,6 +2041,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{719d7b92-c9fb-4135-8b8f-f434c6a7b9bf}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2629,15 +2634,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>1721485</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:colOff>1594485</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2645,7 +2650,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="15513685" y="2057400"/>
+        <a:off x="15386685" y="2241550"/>
         <a:ext cx="4844415" cy="3638550"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3663,7 +3668,7 @@
         <v>100</v>
       </c>
       <c r="G5" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="1">
         <v>10</v>
@@ -3878,7 +3883,7 @@
         <v>200</v>
       </c>
       <c r="G6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="1">
         <v>5</v>
